--- a/agriculture 22.xlsx
+++ b/agriculture 22.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t xml:space="preserve"> 2019-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1998-2020)</t>
@@ -145,7 +148,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]0.00;\(0.00\)"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -175,6 +178,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -240,7 +256,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -265,7 +281,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -286,7 +310,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB1048576"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1341,7 +1365,7 @@
         <v>-3.14451185879757</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>37</v>
       </c>
@@ -1359,24 +1383,43 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-      <c r="AB24" s="6"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A24:AB24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A25:O25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 22.xlsx
+++ b/agriculture 22.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve"> 2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1998-2020)</t>
@@ -148,7 +148,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]0.00;\(0.00\)"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -185,12 +185,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -256,7 +250,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -289,10 +283,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1402,19 +1392,19 @@
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="8"/>
-      <c r="AB25" s="8"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/agriculture 22.xlsx
+++ b/agriculture 22.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve"> 2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1998-2020)</t>
